--- a/InputData/ccs/STfCCE/STfCCE Smoothing Time for CCS Capital Expenditures.xlsx
+++ b/InputData/ccs/STfCCE/STfCCE Smoothing Time for CCS Capital Expenditures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27624"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\STfESCE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1ED16B-9106-404A-9567-24B91C44D363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43DF6B52-ED5C-4DFE-A2DE-4628D1DF86FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="STfCCE" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,35 +39,35 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
+    <t>STfCCE Smoothing Time for CCS Capital Expenditures</t>
+  </si>
+  <si>
     <t>Source:</t>
+  </si>
+  <si>
+    <t>None needed</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>None needed</t>
+    <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to smooth capital costs in the CCS module</t>
+  </si>
+  <si>
+    <t>over a set number of years.</t>
   </si>
   <si>
     <t>Smoothing Time (years)</t>
   </si>
   <si>
-    <t>over a set number of years.</t>
-  </si>
-  <si>
     <t>capital expenditures</t>
   </si>
-  <si>
-    <t>This variable is used with Vensim's DEPRECIATE STRAIGHTLINE function to smooth capital costs in the CCS module</t>
-  </si>
-  <si>
-    <t>STfCCE Smoothing Time for CCS Capital Expenditures</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,108 +433,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" s="4"/>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2">
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2">
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
@@ -548,20 +550,20 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="29.1">
       <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="5">
         <v>3</v>
@@ -570,4 +572,165 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6BAAC53-2820-48AC-8CFD-6A44635108F0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5908D164-232D-40F6-916E-0912A5CC9545}"/>
 </file>